--- a/data/aa2_3_e.xlsx
+++ b/data/aa2_3_e.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GinrutPrices\Output\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\odelyas\Desktop\AA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,16 +15,16 @@
     <sheet name="AA.2.3" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">AA.2.3!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">AA.2.3!$5:$8</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
-  <si>
-    <t>Last produced for Price Statistics Monthly No. 4/2026, Central Bureau of Statistics</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="125">
+  <si>
+    <t>Last produced for Price Statistics Monthly No. 7/2026, Central Bureau of Statistics</t>
   </si>
   <si>
     <t>Base: October 2017 - November 2017=414.5</t>
@@ -369,6 +369,15 @@
   </si>
   <si>
     <t>February 2026 - March 2026</t>
+  </si>
+  <si>
+    <t>March 2026 - April 2026</t>
+  </si>
+  <si>
+    <t>April 2026 - May 2026</t>
+  </si>
+  <si>
+    <t>May 2026 - June 2026</t>
   </si>
   <si>
     <t>(1)    These indices serve as indicators of changes in prices of dwellings by district and are not part of the Consumer Price Index framework.</t>
@@ -429,17 +438,20 @@
       <sz val="12"/>
       <color indexed="16"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="18"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -449,11 +461,13 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -488,59 +502,11 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -611,6 +577,54 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="double">
@@ -625,40 +639,28 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -670,6 +672,18 @@
     <xf numFmtId="174" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -678,9 +692,6 @@
     </xf>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -691,20 +702,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultColWidth="4.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="30" style="8" customWidth="1"/>
@@ -1005,101 +1019,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
     </row>
     <row r="3" spans="1:13" ht="18.75">
-      <c r="A3" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
+      <c r="A3" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4"/>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" spans="1:13" ht="22.5">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="25" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="25" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="25" t="s">
+      <c r="I6" s="25"/>
+      <c r="J6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="25" t="s">
+      <c r="K6" s="25"/>
+      <c r="L6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="27"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="22.5">
       <c r="A7" s="5"/>
@@ -5177,40 +5191,40 @@
       <c r="A107" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>597.4</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="14">
         <v>-0.6</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>662.9</v>
       </c>
-      <c r="E107" s="15">
+      <c r="E107" s="14">
         <v>0</v>
       </c>
-      <c r="F107" s="11">
+      <c r="F107" s="10">
         <v>626</v>
       </c>
-      <c r="G107" s="15">
+      <c r="G107" s="14">
         <v>0.3</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="10">
         <v>586.4</v>
       </c>
-      <c r="I107" s="15">
+      <c r="I107" s="14">
         <v>-0.5</v>
       </c>
-      <c r="J107" s="11">
+      <c r="J107" s="10">
         <v>569.79999999999995</v>
       </c>
-      <c r="K107" s="15">
+      <c r="K107" s="14">
         <v>0.3</v>
       </c>
-      <c r="L107" s="11">
+      <c r="L107" s="10">
         <v>580.29999999999995</v>
       </c>
-      <c r="M107" s="18">
+      <c r="M107" s="17">
         <v>0.2</v>
       </c>
     </row>
@@ -5218,237 +5232,368 @@
       <c r="A108" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B108" s="11">
-        <v>591.4</v>
-      </c>
-      <c r="C108" s="15">
-        <v>-1</v>
-      </c>
-      <c r="D108" s="11">
-        <v>668.9</v>
-      </c>
-      <c r="E108" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="F108" s="11">
-        <v>627.9</v>
-      </c>
-      <c r="G108" s="15">
+      <c r="B108" s="10">
+        <v>589</v>
+      </c>
+      <c r="C108" s="14">
+        <v>-1.4</v>
+      </c>
+      <c r="D108" s="10">
+        <v>669.5</v>
+      </c>
+      <c r="E108" s="14">
+        <v>1</v>
+      </c>
+      <c r="F108" s="10">
+        <v>629.1</v>
+      </c>
+      <c r="G108" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="H108" s="10">
+        <v>590.5</v>
+      </c>
+      <c r="I108" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="J108" s="10">
+        <v>565.20000000000005</v>
+      </c>
+      <c r="K108" s="14">
+        <v>-0.8</v>
+      </c>
+      <c r="L108" s="10">
+        <v>582</v>
+      </c>
+      <c r="M108" s="17">
         <v>0.3</v>
-      </c>
-      <c r="H108" s="11">
-        <v>589.9</v>
-      </c>
-      <c r="I108" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="J108" s="11">
-        <v>565.20000000000005</v>
-      </c>
-      <c r="K108" s="15">
-        <v>-0.8</v>
-      </c>
-      <c r="L108" s="11">
-        <v>581.5</v>
-      </c>
-      <c r="M108" s="18">
-        <v>0.2</v>
       </c>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="11">
-        <v>593.79999999999995</v>
-      </c>
-      <c r="C109" s="15">
+      <c r="B109" s="10">
+        <v>591.9</v>
+      </c>
+      <c r="C109" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="D109" s="10">
+        <v>667.5</v>
+      </c>
+      <c r="E109" s="14">
+        <v>-0.3</v>
+      </c>
+      <c r="F109" s="10">
+        <v>631.6</v>
+      </c>
+      <c r="G109" s="14">
         <v>0.4</v>
       </c>
-      <c r="D109" s="11">
-        <v>668.2</v>
-      </c>
-      <c r="E109" s="15">
+      <c r="H109" s="10">
+        <v>590.5</v>
+      </c>
+      <c r="I109" s="14">
+        <v>0</v>
+      </c>
+      <c r="J109" s="10">
+        <v>572.5</v>
+      </c>
+      <c r="K109" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L109" s="10">
+        <v>579.70000000000005</v>
+      </c>
+      <c r="M109" s="17">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="11">
+        <v>576.5</v>
+      </c>
+      <c r="C110" s="15">
+        <v>-2.6</v>
+      </c>
+      <c r="D110" s="11">
+        <v>665.5</v>
+      </c>
+      <c r="E110" s="15">
+        <v>-0.3</v>
+      </c>
+      <c r="F110" s="11">
+        <v>621.5</v>
+      </c>
+      <c r="G110" s="15">
+        <v>-1.6</v>
+      </c>
+      <c r="H110" s="11">
+        <v>589.9</v>
+      </c>
+      <c r="I110" s="15">
         <v>-0.1</v>
       </c>
-      <c r="F109" s="11">
-        <v>628.5</v>
-      </c>
-      <c r="G109" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="H109" s="11">
-        <v>588.70000000000005</v>
-      </c>
-      <c r="I109" s="15">
-        <v>-0.2</v>
-      </c>
-      <c r="J109" s="11">
-        <v>572</v>
-      </c>
-      <c r="K109" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="L109" s="11">
-        <v>581.5</v>
-      </c>
-      <c r="M109" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13">
-      <c r="A110" s="7"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12"/>
-      <c r="E110" s="12"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="12"/>
-      <c r="I110" s="12"/>
-      <c r="J110" s="12"/>
-      <c r="K110" s="12"/>
-      <c r="L110" s="12"/>
-      <c r="M110" s="12"/>
+      <c r="J110" s="11">
+        <v>578.79999999999995</v>
+      </c>
+      <c r="K110" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L110" s="11">
+        <v>573.29999999999995</v>
+      </c>
+      <c r="M110" s="18">
+        <v>-1.1000000000000001</v>
+      </c>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19"/>
-      <c r="F111" s="19"/>
-      <c r="G111" s="19"/>
-      <c r="H111" s="19"/>
-      <c r="I111" s="19"/>
-      <c r="J111" s="19"/>
-      <c r="K111" s="19"/>
-      <c r="L111" s="19"/>
-      <c r="M111" s="19"/>
+      <c r="A111" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="11">
+        <v>567.29999999999995</v>
+      </c>
+      <c r="C111" s="15">
+        <v>-1.6</v>
+      </c>
+      <c r="D111" s="11">
+        <v>661.5</v>
+      </c>
+      <c r="E111" s="15">
+        <v>-0.6</v>
+      </c>
+      <c r="F111" s="11">
+        <v>617.79999999999995</v>
+      </c>
+      <c r="G111" s="15">
+        <v>-0.6</v>
+      </c>
+      <c r="H111" s="11">
+        <v>588.1</v>
+      </c>
+      <c r="I111" s="15">
+        <v>-0.3</v>
+      </c>
+      <c r="J111" s="11">
+        <v>564.29999999999995</v>
+      </c>
+      <c r="K111" s="15">
+        <v>-2.5</v>
+      </c>
+      <c r="L111" s="11">
+        <v>571.6</v>
+      </c>
+      <c r="M111" s="18">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="19"/>
-      <c r="I112" s="19"/>
-      <c r="J112" s="19"/>
-      <c r="K112" s="19"/>
-      <c r="L112" s="19"/>
-      <c r="M112" s="19"/>
+      <c r="A112" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="11">
+        <v>577.5</v>
+      </c>
+      <c r="C112" s="15">
+        <v>1.8</v>
+      </c>
+      <c r="D112" s="11">
+        <v>667.5</v>
+      </c>
+      <c r="E112" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="F112" s="11">
+        <v>627.1</v>
+      </c>
+      <c r="G112" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="H112" s="11">
+        <v>582.20000000000005</v>
+      </c>
+      <c r="I112" s="15">
+        <v>-1</v>
+      </c>
+      <c r="J112" s="11">
+        <v>560.29999999999995</v>
+      </c>
+      <c r="K112" s="15">
+        <v>-0.7</v>
+      </c>
+      <c r="L112" s="11">
+        <v>575.6</v>
+      </c>
+      <c r="M112" s="18">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="19"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="19"/>
-      <c r="I113" s="19"/>
-      <c r="J113" s="19"/>
-      <c r="K113" s="19"/>
-      <c r="L113" s="19"/>
-      <c r="M113" s="19"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="12"/>
+      <c r="L113" s="12"/>
+      <c r="M113" s="12"/>
     </row>
     <row r="114" spans="1:13">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19"/>
-      <c r="F114" s="19"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="19"/>
-      <c r="I114" s="19"/>
-      <c r="J114" s="19"/>
-      <c r="K114" s="19"/>
-      <c r="L114" s="19"/>
-      <c r="M114" s="19"/>
+      <c r="B114" s="27"/>
+      <c r="C114" s="27"/>
+      <c r="D114" s="27"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="27"/>
+      <c r="G114" s="27"/>
+      <c r="H114" s="27"/>
+      <c r="I114" s="27"/>
+      <c r="J114" s="27"/>
+      <c r="K114" s="27"/>
+      <c r="L114" s="27"/>
+      <c r="M114" s="27"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="19" t="s">
+      <c r="A115" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="19"/>
-      <c r="F115" s="19"/>
-      <c r="G115" s="19"/>
-      <c r="H115" s="19"/>
-      <c r="I115" s="19"/>
-      <c r="J115" s="19"/>
-      <c r="K115" s="19"/>
-      <c r="L115" s="19"/>
-      <c r="M115" s="19"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27"/>
+      <c r="H115" s="27"/>
+      <c r="I115" s="27"/>
+      <c r="J115" s="27"/>
+      <c r="K115" s="27"/>
+      <c r="L115" s="27"/>
+      <c r="M115" s="27"/>
     </row>
     <row r="116" spans="1:13">
-      <c r="A116" s="19" t="s">
+      <c r="A116" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-      <c r="D116" s="19"/>
-      <c r="E116" s="19"/>
-      <c r="F116" s="19"/>
-      <c r="G116" s="19"/>
-      <c r="H116" s="19"/>
-      <c r="I116" s="19"/>
-      <c r="J116" s="19"/>
-      <c r="K116" s="19"/>
-      <c r="L116" s="19"/>
-      <c r="M116" s="19"/>
+      <c r="B116" s="27"/>
+      <c r="C116" s="27"/>
+      <c r="D116" s="27"/>
+      <c r="E116" s="27"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="27"/>
+      <c r="H116" s="27"/>
+      <c r="I116" s="27"/>
+      <c r="J116" s="27"/>
+      <c r="K116" s="27"/>
+      <c r="L116" s="27"/>
+      <c r="M116" s="27"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="19" t="s">
+      <c r="A117" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-      <c r="D117" s="19"/>
-      <c r="E117" s="19"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
-      <c r="H117" s="19"/>
-      <c r="I117" s="19"/>
-      <c r="J117" s="19"/>
-      <c r="K117" s="19"/>
-      <c r="L117" s="19"/>
-      <c r="M117" s="19"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="27"/>
+      <c r="D117" s="27"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27"/>
+      <c r="G117" s="27"/>
+      <c r="H117" s="27"/>
+      <c r="I117" s="27"/>
+      <c r="J117" s="27"/>
+      <c r="K117" s="27"/>
+      <c r="L117" s="27"/>
+      <c r="M117" s="27"/>
     </row>
     <row r="118" spans="1:13">
-      <c r="A118" s="19" t="s">
+      <c r="A118" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19"/>
-      <c r="I118" s="19"/>
-      <c r="J118" s="19"/>
-      <c r="K118" s="19"/>
-      <c r="L118" s="19"/>
-      <c r="M118" s="19"/>
+      <c r="B118" s="27"/>
+      <c r="C118" s="27"/>
+      <c r="D118" s="27"/>
+      <c r="E118" s="27"/>
+      <c r="F118" s="27"/>
+      <c r="G118" s="27"/>
+      <c r="H118" s="27"/>
+      <c r="I118" s="27"/>
+      <c r="J118" s="27"/>
+      <c r="K118" s="27"/>
+      <c r="L118" s="27"/>
+      <c r="M118" s="27"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" s="27"/>
+      <c r="C119" s="27"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="27"/>
+      <c r="I119" s="27"/>
+      <c r="J119" s="27"/>
+      <c r="K119" s="27"/>
+      <c r="L119" s="27"/>
+      <c r="M119" s="27"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="27"/>
+      <c r="C120" s="27"/>
+      <c r="D120" s="27"/>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27"/>
+      <c r="G120" s="27"/>
+      <c r="H120" s="27"/>
+      <c r="I120" s="27"/>
+      <c r="J120" s="27"/>
+      <c r="K120" s="27"/>
+      <c r="L120" s="27"/>
+      <c r="M120" s="27"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="27"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="27"/>
+      <c r="H121" s="27"/>
+      <c r="I121" s="27"/>
+      <c r="J121" s="27"/>
+      <c r="K121" s="27"/>
+      <c r="L121" s="27"/>
+      <c r="M121" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A119:M119"/>
+    <mergeCell ref="A120:M120"/>
+    <mergeCell ref="A121:M121"/>
+    <mergeCell ref="A114:M114"/>
+    <mergeCell ref="A115:M115"/>
+    <mergeCell ref="A116:M116"/>
+    <mergeCell ref="A117:M117"/>
+    <mergeCell ref="A118:M118"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A4:M4"/>
@@ -5459,14 +5604,6 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A116:M116"/>
-    <mergeCell ref="A117:M117"/>
-    <mergeCell ref="A118:M118"/>
-    <mergeCell ref="A111:M111"/>
-    <mergeCell ref="A112:M112"/>
-    <mergeCell ref="A113:M113"/>
-    <mergeCell ref="A114:M114"/>
-    <mergeCell ref="A115:M115"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.5"/>
